--- a/out/MLP_Base_repeat_4_000006.xlsx
+++ b/out/MLP_Base_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.967222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004406049147867598</v>
+        <v>-0.0003128222096160753</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5670928468015957</v>
+        <v>0.4026263409910837</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.13525890605684</v>
+        <v>0.806015066578293</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1309650476743587</v>
+        <v>-0.09298306858678258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.967222099549092</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4356871942124502</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.967222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4356871942124502</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.967222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4351846226012414</v>
+        <v>0.3090611464411744</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.544008680454898</v>
+        <v>0.8273593729251539</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.526276465671773</v>
+        <v>1.965427358179969</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2954286015532641</v>
+        <v>0.158305831513631</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.570871934188153</v>
+        <v>1.453472403560454</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.5174714310413512</v>
+        <v>0.2772878948554011</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.367222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.310530887413567</v>
+        <v>1.849819837926228</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2833859484698871</v>
+        <v>0.1518529418944903</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.367222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.359385801166208</v>
+        <v>1.875998821448659</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.117042523749068</v>
+        <v>0.06271747648045552</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.367222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.309787740357486</v>
+        <v>1.849421643296335</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1458254310987602</v>
+        <v>0.07814059364344086</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.367222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.484415330312894</v>
+        <v>1.94299588095038</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.08780574613746048</v>
+        <v>0.04705014038626072</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.514102434471763</v>
+        <v>1.958903724088574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.06675507371164703</v>
+        <v>0.03577165311867397</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.367222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.559771112752722</v>
+        <v>1.983375603149405</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02952594282738612</v>
+        <v>0.01582110087575931</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.552008840395874</v>
+        <v>1.979216191904165</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02342905797767721</v>
+        <v>0.01255309261819042</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.56933131392472</v>
+        <v>1.988497582471814</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01161687730331525</v>
+        <v>0.006223685855629567</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.367222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.569118871502583</v>
+        <v>1.988381415888184</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006753073332097424</v>
+        <v>0.003616954928308779</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.367222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.57100241067055</v>
+        <v>1.989388350043265</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003375491266421527</v>
+        <v>0.001804522863781575</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.570993201730722</v>
+        <v>1.989381097065147</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001665170582343769</v>
+        <v>0.0008890155785007095</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.570945923040071</v>
+        <v>1.989353431364695</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0009629193055917935</v>
+        <v>0.000515673833352827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.571209052212015</v>
+        <v>1.989492417003745</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003186356665259266</v>
+        <v>0.0001690936688898088</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.570881504756307</v>
+        <v>1.989314504212841</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001589427537507861</v>
+        <v>8.258585474357068e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.57087831881898</v>
+        <v>1.989310473369611</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>8.306306068390622e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.570887855587678</v>
+        <v>1.989313240302476</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.766324804533871e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.570879986086354</v>
+        <v>1.989306688416747</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.118280671066587e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.367222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.570885207177095</v>
+        <v>1.989307066984992</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>7.887479732251461e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.570876870025726</v>
+        <v>1.989300400021122</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.967222099549092</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.570873765340477</v>
+        <v>1.989296537946026</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.570869446349326</v>
+        <v>1.989291990633841</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.434846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.570864622176438</v>
+        <v>1.989292080578491</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.570863764242853</v>
+        <v>1.989291222644906</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.570863992563888</v>
+        <v>1.989291450965941</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.570863196899676</v>
+        <v>1.989290655301729</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.570863259169049</v>
+        <v>1.989290717571102</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.570863286844325</v>
+        <v>1.989290745246379</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.570863439058348</v>
+        <v>1.989290897460402</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.570863093117387</v>
+        <v>1.98929055151944</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.570863169224398</v>
+        <v>1.989290627626452</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.57086333527606</v>
+        <v>1.989290793678113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.570863695054661</v>
+        <v>1.989291153456713</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.570863715811118</v>
+        <v>1.989291174213171</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.570863819593406</v>
+        <v>1.989291277995459</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.434846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.570864047914441</v>
+        <v>1.989291506316494</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.434846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.570863923375695</v>
+        <v>1.989291381777748</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.570863951050971</v>
+        <v>1.989291409453025</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.570864006401526</v>
+        <v>1.989291464803579</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.570864269316656</v>
+        <v>1.989291727718709</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.570864186290826</v>
+        <v>1.989291644692879</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.570863978726249</v>
+        <v>1.989291437128302</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.570863992563888</v>
+        <v>1.989291450965941</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.570864130940271</v>
+        <v>1.989291589342325</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.570863847268684</v>
+        <v>1.989291305670736</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.570863674298203</v>
+        <v>1.989291132700256</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.570863570515914</v>
+        <v>1.989291028917967</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.570863715811118</v>
+        <v>1.989291174213171</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.570863957969791</v>
+        <v>1.989291416371844</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.57086378499931</v>
+        <v>1.989291243401363</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.570863487490083</v>
+        <v>1.989290945892137</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.570863473652445</v>
+        <v>1.989290932054498</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.570863106955025</v>
+        <v>1.989290565357078</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.570863106955025</v>
+        <v>1.989290565357078</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.570863044685653</v>
+        <v>1.989290503087705</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.570862940903364</v>
+        <v>1.989290399305417</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.570862767932883</v>
+        <v>1.989290226334936</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.570862816364618</v>
+        <v>1.989290274766671</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.570862456586017</v>
+        <v>1.989289914988071</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.570862415073103</v>
+        <v>1.989289873475155</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.570862470423656</v>
+        <v>1.989289928825709</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.57086252577421</v>
+        <v>1.989289984176263</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.570862567287126</v>
+        <v>1.989290025689179</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.570862297453175</v>
+        <v>1.989289755855228</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.570862352803729</v>
+        <v>1.989289811205782</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.570862498098933</v>
+        <v>1.989289956500986</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.570862463504837</v>
+        <v>1.98928992190689</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.570862449667199</v>
+        <v>1.989289908069252</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.570862539611848</v>
+        <v>1.989289998013902</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.967222099549092</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.570862857877533</v>
+        <v>1.989290316279586</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.570862677988233</v>
+        <v>1.989290136390286</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.570862719501149</v>
+        <v>1.989290177903202</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.570862532693029</v>
+        <v>1.989289991095082</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.570862601881222</v>
+        <v>1.989290060283274</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.570862401235464</v>
+        <v>1.989289859637517</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.570862442748379</v>
+        <v>1.989289901150432</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.034846904977811</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.570862470423656</v>
+        <v>1.989289928825709</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000006.xlsx
+++ b/out/MLP_Base_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.967222099549092</v>
+        <v>0.2337207519070788</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004406049147867598</v>
+        <v>-0.0003283101106196409</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5670928468015957</v>
+        <v>0.4225604760321078</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.13525890605684</v>
+        <v>0.8459210616327142</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1309650476743587</v>
+        <v>-0.09758667972509802</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4356871942124502</v>
+        <v>0.3246454861963899</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4356871942124502</v>
+        <v>0.3246454861963899</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4351846226012414</v>
+        <v>0.3242909914390659</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.544008680454898</v>
+        <v>1.089084560839445</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.526276465671773</v>
+        <v>2.504628735028066</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2954286015532641</v>
+        <v>0.2083839971922626</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.570871934188153</v>
+        <v>1.830722987160274</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.5174714310413512</v>
+        <v>0.3650043338224168</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.367222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.310530887413567</v>
+        <v>2.352450117192622</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2833859484698871</v>
+        <v>0.1998898941882815</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.367222099549092</v>
+        <v>1.788952296833663</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.359385801166208</v>
+        <v>2.386910524616876</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.117042523749068</v>
+        <v>0.08255724054239082</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.367222099549092</v>
+        <v>1.788952296833663</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.309787740357486</v>
+        <v>2.351925958592225</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1458254310987602</v>
+        <v>0.1028597275508554</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.367222099549092</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.484415330312894</v>
+        <v>2.475101636458117</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.08780574613746048</v>
+        <v>0.06193425202754487</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.514102434471763</v>
+        <v>2.49604179458758</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.06675507371164703</v>
+        <v>0.04708668121766708</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.367222099549092</v>
+        <v>0.2337207519070788</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.559771112752722</v>
+        <v>2.52825505550673</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02952594282738612</v>
+        <v>0.02082735603337305</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070788</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.552008840395874</v>
+        <v>2.52277975915708</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02342905797767721</v>
+        <v>0.01652540314094882</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.56933131392472</v>
+        <v>2.534998231919802</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01161687730331525</v>
+        <v>0.008192350822850639</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.367222099549092</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.569118871502583</v>
+        <v>2.534846908796054</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006753073332097424</v>
+        <v>0.004763180022086817</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.367222099549092</v>
+        <v>1.788952296833663</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.57100241067055</v>
+        <v>2.536174085567282</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003375491266421527</v>
+        <v>0.002377635410670594</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.570993201730722</v>
+        <v>2.536166119025354</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001665170582343769</v>
+        <v>0.001173605746576498</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.967222099549092</v>
+        <v>1.988952296833663</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.570945923040071</v>
+        <v>2.536131283804757</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0009629193055917935</v>
+        <v>0.000679218819470061</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.967222099549092</v>
+        <v>1.211336524370371</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.571209052212015</v>
+        <v>2.536315495702227</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003186356665259266</v>
+        <v>0.0002226609516251346</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.570881504756307</v>
+        <v>2.536083271964582</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001589427537507861</v>
+        <v>0.0001095353485108232</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.57087831881898</v>
+        <v>2.536079553161074</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>8.306306068390622e-05</v>
+        <v>5.860109938282116e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.570887855587678</v>
+        <v>2.536084907027643</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.766324804533871e-05</v>
+        <v>2.58123458105224e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.570879986086354</v>
+        <v>2.536077889576194</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.118280671066587e-05</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.367222099549092</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.570885207177095</v>
+        <v>2.536079883525988</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>7.887479732251461e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.034846904977811</v>
+        <v>1.011336524370371</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.570876870025726</v>
+        <v>2.536072549131844</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.967222099549092</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.570873765340477</v>
+        <v>2.536069063911536</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.570869446349326</v>
+        <v>2.536064516599351</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.570864622176438</v>
+        <v>2.536064606544001</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.570863764242853</v>
+        <v>2.536063748610416</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.570863992563888</v>
+        <v>2.536063976931451</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.967222099549092</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.570863196899676</v>
+        <v>2.536063181267239</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.570863259169049</v>
+        <v>2.536063243536612</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.570863286844325</v>
+        <v>2.536063271211889</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.570863439058348</v>
+        <v>2.536063423425912</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.570863093117387</v>
+        <v>2.53606307748495</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.570863169224398</v>
+        <v>2.536063153591962</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.57086333527606</v>
+        <v>2.536063319643624</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.570863695054661</v>
+        <v>2.536063679422223</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.2337207519070787</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.570863715811118</v>
+        <v>2.536063700178681</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.967222099549092</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.570863819593406</v>
+        <v>2.53606380396097</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.570864047914441</v>
+        <v>2.536064032282005</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.570863923375695</v>
+        <v>2.536063907743258</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.570863951050971</v>
+        <v>2.536063935418535</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.570864006401526</v>
+        <v>2.536063990769089</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.570864269316656</v>
+        <v>2.53606425368422</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.570864186290826</v>
+        <v>2.536064170658389</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.570863978726249</v>
+        <v>2.536063963093812</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.570863992563888</v>
+        <v>2.536063976931451</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.570864130940271</v>
+        <v>2.536064115307835</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.570863847268684</v>
+        <v>2.536063831636247</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.570863674298203</v>
+        <v>2.536063658665766</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.570863570515914</v>
+        <v>2.536063554883478</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.570863715811118</v>
+        <v>2.536063700178681</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.570863957969791</v>
+        <v>2.536063942337355</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.57086378499931</v>
+        <v>2.536063769366874</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.570863487490083</v>
+        <v>2.536063471857647</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.570863473652445</v>
+        <v>2.536063458020008</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.570863106955025</v>
+        <v>2.536063091322589</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.570863106955025</v>
+        <v>2.536063091322589</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.570863044685653</v>
+        <v>2.536063029053216</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.570862940903364</v>
+        <v>2.536062925270927</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.570862767932883</v>
+        <v>2.536062752300446</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.570862816364618</v>
+        <v>2.536062800732181</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.570862456586017</v>
+        <v>2.536062440953581</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.570862415073103</v>
+        <v>2.536062399440666</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.570862470423656</v>
+        <v>2.53606245479122</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.57086252577421</v>
+        <v>2.536062510141774</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.570862567287126</v>
+        <v>2.536062551654689</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.570862297453175</v>
+        <v>2.536062281820739</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.570862352803729</v>
+        <v>2.536062337171292</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.570862498098933</v>
+        <v>2.536062482466496</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.570862463504837</v>
+        <v>2.5360624478724</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.570862449667199</v>
+        <v>2.536062434034762</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.034846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.570862539611848</v>
+        <v>2.536062523979412</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.967222099549092</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.570862857877533</v>
+        <v>2.536062842245096</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.434846904977811</v>
+        <v>0.4337207519070788</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.570862677988233</v>
+        <v>2.536062662355796</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.434846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.570862719501149</v>
+        <v>2.536062703868712</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.3438950205562133</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.570862532693029</v>
+        <v>2.536062517060593</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.570862601881222</v>
+        <v>2.536062586248785</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.570862401235464</v>
+        <v>2.536062385603028</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.570862442748379</v>
+        <v>2.536062427115943</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.034846904977811</v>
+        <v>-0.5438950205562134</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.570862470423656</v>
+        <v>2.53606245479122</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000006.xlsx
+++ b/out/MLP_Base_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4137636721134186</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4162095189094543</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4329825937747955</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4590980410575867</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4179244637489319</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4407932758331299</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3935829401016235</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4508934617042542</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4548958539962769</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4173209369182587</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3935754597187042</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3746608197689056</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4205873012542725</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3853292167186737</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3774158656597137</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3734360635280609</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4007578492164612</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4235558211803436</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4644958972930908</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4197490811347961</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4054184854030609</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.380696028470993</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3864334523677826</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4460949301719666</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3953458964824677</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4716559052467346</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5687888264656067</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.211336524370371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5049721002578735</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.211336524370371</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.454785019159317</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4576185643672943</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3438950205562133</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4098453521728516</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3875474035739899</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4100253283977509</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5166712999343872</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2337207519070788</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4620971083641052</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4547322690486908</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4842861592769623</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4337615370750427</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4512077867984772</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4893905520439148</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2337207519070787</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5355809330940247</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.211336524370371</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5565968751907349</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.988952296833663</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6143795251846313</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.988952296833663</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003283101106196409</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4225604760321078</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5871128439903259</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.988952296833663</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8459210616327142</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09758667972509802</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5157287120819092</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.988952296833663</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3246454861963899</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5557451844215393</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.988952296833663</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3246454861963899</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5485588908195496</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.988952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3242909914390659</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.089084560839445</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5000009536743164</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.988952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.504628735028066</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2083839971922626</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5697134137153625</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.988952296833663</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.830722987160274</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3650043338224168</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5441634654998779</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.988952296833663</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.352450117192622</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1998898941882815</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5506820678710938</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.788952296833663</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.386910524616876</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08255724054239082</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.515775740146637</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.788952296833663</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.351925958592225</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1028597275508554</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.614447295665741</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.011336524370371</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.475101636458117</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06193425202754487</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4976601898670197</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.011336524370371</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.49604179458758</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04708668121766708</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6477514505386353</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2337207519070788</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.52825505550673</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02082735603337305</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4156978130340576</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2337207519070788</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.52277975915708</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01652540314094882</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3192143142223358</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.534998231919802</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008192350822850639</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7246528267860413</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.011336524370371</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.534846908796054</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004763180022086817</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7091462016105652</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.788952296833663</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.536174085567282</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002377635410670594</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5753724575042725</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.988952296833663</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.536166119025354</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001173605746576498</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5520262718200684</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.988952296833663</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.536131283804757</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000679218819470061</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5819427967071533</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.211336524370371</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.536315495702227</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002226609516251346</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4905843734741211</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4337207519070788</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.536083271964582</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001095353485108232</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.496174156665802</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.536079553161074</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.860109938282116e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4530595541000366</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.536084907027643</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4889488518238068</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.536077889576194</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.5147673487663269</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.536079883525988</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4872404336929321</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.011336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.536072549131844</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.5136295557022095</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.536069063911536</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4314243793487549</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4337207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.536064516599351</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4543516933917999</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.536064606544001</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4443774819374084</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.536063748610416</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4792379438877106</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.536063976931451</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5027281641960144</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.536063181267239</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4269361197948456</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4337207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.536063243536612</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4372660517692566</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.536063271211889</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4739804267883301</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.536063423425912</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4255280494689941</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.53606307748495</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4353740215301514</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.536063153591962</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3890161216259003</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.536063319643624</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4637623727321625</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.536063679422223</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4886029362678528</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2337207519070787</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.536063700178681</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5092619061470032</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4337207519070788</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.53606380396097</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4226087629795074</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4337207519070788</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.536064032282005</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3954541087150574</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3438950205562133</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.536063907743258</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3611833155155182</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3438950205562133</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.536063935418535</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4539044499397278</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.536063990769089</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3976262509822845</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.53606425368422</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4025250971317291</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.536064170658389</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3812273740768433</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.536063963093812</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3725425601005554</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.536063976931451</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3660334944725037</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.536064115307835</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3683686256408691</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.536063831636247</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3548395335674286</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.536063658665766</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4159503579139709</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.536063554883478</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3799537122249603</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.536063700178681</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3525553643703461</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.536063942337355</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3677967488765717</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.536063769366874</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3533484935760498</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.536063471857647</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3816428780555725</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.536063458020008</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3705423176288605</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.536063091322589</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3922681212425232</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.536063091322589</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4503599405288696</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.536063029053216</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3808083236217499</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.536062925270927</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3899750411510468</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.536062752300446</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4035957157611847</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.536062800732181</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.399506539106369</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.536062440953581</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3866044282913208</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.536062399440666</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4171398878097534</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.53606245479122</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3710827827453613</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.536062510141774</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.378227025270462</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.536062551654689</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3820550143718719</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.536062281820739</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3856576681137085</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.536062337171292</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3744241297245026</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.536062482466496</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3779880106449127</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.5360624478724</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3703631460666656</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.536062434034762</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4362221956253052</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.536062523979412</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5235403776168823</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.536062842245096</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4388798773288727</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4337207519070788</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.536062662355796</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.425060510635376</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3438950205562133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.536062703868712</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4251587390899658</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3438950205562133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.536062517060593</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3899068534374237</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5438950205562134</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.536062586248785</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4163834750652313</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.536062385603028</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3895744979381561</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.536062427115943</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4095234572887421</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5438950205562134</v>
+        <v>-0.7200000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.53606245479122</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>
